--- a/docs/d/109/inyear.xlsx
+++ b/docs/d/109/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 69 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 66 clubs short</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6484,8 +6484,8 @@
       <c r="Y56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" s="9" t="n">
-        <v>0</v>
+      <c r="Z56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA56" s="10" t="n">
         <v>1</v>
@@ -8322,7 +8322,7 @@
         <v>0</v>
       </c>
       <c r="S74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T74" s="9" t="n">
         <v>0</v>
@@ -8688,7 +8688,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8758,8 +8758,8 @@
       <c r="Y78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z78" s="9" t="n">
-        <v>0</v>
+      <c r="Z78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA78" s="10" t="n">
         <v>1</v>
@@ -12362,7 +12362,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="P114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q114" s="9" t="n">
         <v>0</v>
@@ -12414,8 +12414,8 @@
       <c r="S114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T114" s="9" t="n">
-        <v>0</v>
+      <c r="T114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U114" s="9" t="n">
         <v>0</v>
@@ -13697,7 +13697,7 @@
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13767,8 +13767,8 @@
       <c r="Y127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z127" s="9" t="n">
-        <v>0</v>
+      <c r="Z127" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA127" s="10" t="n">
         <v>1</v>
@@ -13816,13 +13816,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>0</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
@@ -16571,7 +16571,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -16769,7 +16769,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -17033,7 +17033,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -17132,7 +17132,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>

--- a/docs/d/109/inyear.xlsx
+++ b/docs/d/109/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,11 @@
       <c r="AB6" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC6" s="4" t="inlineStr"/>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1444,7 +1448,11 @@
       <c r="AB7" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC7" s="4" t="inlineStr"/>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1650,7 +1658,11 @@
       <c r="AB9" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC9" s="4" t="inlineStr"/>
+      <c r="AC9" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1852,7 +1864,11 @@
       <c r="AB11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC11" s="4" t="inlineStr"/>
+      <c r="AC11" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -3193,7 +3209,11 @@
       <c r="AB24" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC24" s="4" t="inlineStr"/>
+      <c r="AC24" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -3294,7 +3314,11 @@
       <c r="AB25" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC25" s="4" t="inlineStr"/>
+      <c r="AC25" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -3395,7 +3419,11 @@
       <c r="AB26" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC26" s="4" t="inlineStr"/>
+      <c r="AC26" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -3496,7 +3524,11 @@
       <c r="AB27" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC27" s="4" t="inlineStr"/>
+      <c r="AC27" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -3597,7 +3629,11 @@
       <c r="AB28" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC28" s="4" t="inlineStr"/>
+      <c r="AC28" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -7321,7 +7357,11 @@
       <c r="AB64" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC64" s="4" t="inlineStr"/>
+      <c r="AC64" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -7632,7 +7672,11 @@
       <c r="AB67" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC67" s="4" t="inlineStr"/>
+      <c r="AC67" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -7733,7 +7777,11 @@
       <c r="AB68" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC68" s="4" t="inlineStr"/>
+      <c r="AC68" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -8666,7 +8714,11 @@
       <c r="AB77" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC77" s="4" t="inlineStr"/>
+      <c r="AC77" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -9280,7 +9332,11 @@
       <c r="AB83" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC83" s="4" t="inlineStr"/>
+      <c r="AC83" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -9987,7 +10043,11 @@
       <c r="AB90" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC90" s="4" t="inlineStr"/>
+      <c r="AC90" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -10290,7 +10350,11 @@
       <c r="AB93" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC93" s="4" t="inlineStr"/>
+      <c r="AC93" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -11211,7 +11275,11 @@
       <c r="AB102" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC102" s="4" t="inlineStr"/>
+      <c r="AC102" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -11724,7 +11792,11 @@
       <c r="AB107" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC107" s="4" t="inlineStr"/>
+      <c r="AC107" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -12340,7 +12412,11 @@
       <c r="AB113" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC113" s="4" t="inlineStr"/>
+      <c r="AC113" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -12651,7 +12727,11 @@
       <c r="AB116" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC116" s="4" t="inlineStr"/>
+      <c r="AC116" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -13469,7 +13549,11 @@
       <c r="AB124" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC124" s="4" t="inlineStr"/>
+      <c r="AC124" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -13986,7 +14070,11 @@
       <c r="AB129" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC129" s="4" t="inlineStr"/>
+      <c r="AC129" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -15331,7 +15419,11 @@
       <c r="AB142" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC142" s="4" t="inlineStr"/>
+      <c r="AC142" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
@@ -15432,7 +15524,11 @@
       <c r="AB143" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC143" s="4" t="inlineStr"/>
+      <c r="AC143" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">

--- a/docs/d/109/inyear.xlsx
+++ b/docs/d/109/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 16 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 16 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 66 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 58 clubs short</t>
         </is>
       </c>
     </row>
@@ -4085,13 +4085,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>0</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>0</v>
@@ -6866,7 +6866,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="P60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q60" s="9" t="n">
         <v>0</v>
@@ -6916,10 +6916,10 @@
         <v>0</v>
       </c>
       <c r="S60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U60" s="9" t="n">
         <v>0</v>
@@ -8594,8 +8594,8 @@
       <c r="W76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X76" s="9" t="n">
-        <v>0</v>
+      <c r="X76" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y76" s="9" t="n">
         <v>0</v>
@@ -8699,8 +8699,8 @@
       <c r="W77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X77" s="9" t="n">
-        <v>2</v>
+      <c r="X77" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y77" s="9" t="n">
         <v>0</v>
@@ -9762,7 +9762,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="P88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q88" s="9" t="n">
         <v>1</v>
@@ -9832,8 +9832,8 @@
       <c r="Y88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z88" s="9" t="n">
-        <v>0</v>
+      <c r="Z88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA88" s="10" t="n">
         <v>1</v>
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10850,8 +10850,8 @@
       <c r="Y98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" s="9" t="n">
-        <v>0</v>
+      <c r="Z98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA98" s="10" t="n">
         <v>1</v>
@@ -11091,7 +11091,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11161,8 +11161,8 @@
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -11882,8 +11882,8 @@
       <c r="W108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X108" s="9" t="n">
-        <v>3</v>
+      <c r="X108" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y108" s="9" t="n">
         <v>0</v>
@@ -12753,7 +12753,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12823,8 +12823,8 @@
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="9" t="n">
-        <v>0</v>
+      <c r="Z117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA117" s="10" t="n">
         <v>1</v>
@@ -13235,8 +13235,8 @@
       <c r="Y121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z121" s="9" t="n">
-        <v>0</v>
+      <c r="Z121" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA121" s="9" t="n">
         <v>0</v>
@@ -13991,7 +13991,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -14040,8 +14040,8 @@
       <c r="R129" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="S129" s="9" t="n">
-        <v>1</v>
+      <c r="S129" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T129" s="10" t="n">
         <v>1</v>
@@ -14920,7 +14920,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14934,13 +14934,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>0</v>
       </c>
       <c r="V138" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
@@ -14990,8 +14990,8 @@
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="9" t="n">
-        <v>0</v>
+      <c r="Z138" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA138" s="10" t="n">
         <v>1</v>
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -15305,8 +15305,8 @@
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="9" t="n">
-        <v>0</v>
+      <c r="Z141" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA141" s="10" t="n">
         <v>1</v>
@@ -15651,7 +15651,7 @@
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -15721,8 +15721,8 @@
       <c r="Y145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z145" s="9" t="n">
-        <v>0</v>
+      <c r="Z145" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA145" s="10" t="n">
         <v>1</v>
@@ -16700,7 +16700,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16931,7 +16931,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -16997,7 +16997,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -17030,7 +17030,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -17162,7 +17162,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -17228,7 +17228,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -17294,7 +17294,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -17327,7 +17327,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -17360,7 +17360,7 @@
         <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>

--- a/docs/d/109/inyear.xlsx
+++ b/docs/d/109/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 16 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 16 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 58 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 27 clubs short</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1128,8 +1128,8 @@
       <c r="Y4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" s="9" t="n">
-        <v>0</v>
+      <c r="Z4" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA4" s="10" t="n">
         <v>1</v>
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" s="9" t="n">
         <v>0</v>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1855,8 +1855,8 @@
       <c r="Y11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="9" t="n">
-        <v>0</v>
+      <c r="Z11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA11" s="10" t="n">
         <v>1</v>
@@ -2205,7 +2205,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2275,8 +2275,8 @@
       <c r="Y15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" s="9" t="n">
-        <v>0</v>
+      <c r="Z15" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA15" s="10" t="n">
         <v>1</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2586,8 +2586,8 @@
       <c r="Y18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z18" s="9" t="n">
-        <v>0</v>
+      <c r="Z18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA18" s="10" t="n">
         <v>1</v>
@@ -2718,7 +2718,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2732,13 +2732,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -2788,8 +2788,8 @@
       <c r="Y20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z20" s="9" t="n">
-        <v>0</v>
+      <c r="Z20" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA20" s="10" t="n">
         <v>1</v>
@@ -3099,8 +3099,8 @@
       <c r="Y23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" s="9" t="n">
-        <v>0</v>
+      <c r="Z23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA23" s="9" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3410,8 +3410,8 @@
       <c r="Y26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" s="9" t="n">
-        <v>0</v>
+      <c r="Z26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA26" s="10" t="n">
         <v>1</v>
@@ -3857,11 +3857,11 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>28680222</v>
+        <v>28676170</v>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Reggio Emilia</t>
+          <t>Professional Coaching Lab</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
@@ -3879,25 +3879,25 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M31" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O31" s="7" t="inlineStr">
@@ -3924,13 +3924,13 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X31" s="10" t="n">
-        <v>4</v>
+      <c r="X31" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y31" s="9" t="n">
         <v>0</v>
@@ -3938,11 +3938,11 @@
       <c r="Z31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA31" s="10" t="n">
-        <v>1</v>
+      <c r="AA31" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB31" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC31" s="4" t="inlineStr"/>
     </row>
@@ -3958,15 +3958,15 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>28679616</v>
+        <v>28680222</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Segnalazione Vincente</t>
+          <t>Reggio Emilia</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3980,13 +3980,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
@@ -4031,25 +4031,21 @@
         <v>0</v>
       </c>
       <c r="X32" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z32" s="9" t="n">
-        <v>0</v>
+      <c r="Z32" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA32" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB32" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC32" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -4063,15 +4059,15 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>28676170</v>
+        <v>28679616</v>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>ToastMasters Marche - Villaggio Saggio</t>
+          <t>Segnalazione Vincente</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -4085,25 +4081,25 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L33" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M33" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O33" s="7" t="inlineStr">
@@ -4130,27 +4126,31 @@
         <v>0</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X33" s="9" t="n">
-        <v>0</v>
+      <c r="X33" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="9" t="n">
-        <v>0</v>
+      <c r="Z33" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA33" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB33" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC33" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC33" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4636,8 +4636,8 @@
       <c r="S38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T38" s="9" t="n">
-        <v>0</v>
+      <c r="T38" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U38" s="9" t="n">
         <v>0</v>
@@ -4689,7 +4689,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4759,8 +4759,8 @@
       <c r="Y39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z39" s="9" t="n">
-        <v>0</v>
+      <c r="Z39" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA39" s="10" t="n">
         <v>1</v>
@@ -5064,8 +5064,8 @@
       <c r="W42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X42" s="9" t="n">
-        <v>2</v>
+      <c r="X42" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y42" s="9" t="n">
         <v>0</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5595,8 +5595,8 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5801,8 +5801,8 @@
       <c r="Y49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" s="9" t="n">
-        <v>0</v>
+      <c r="Z49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA49" s="10" t="n">
         <v>1</v>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5989,8 +5989,8 @@
       <c r="S51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T51" s="9" t="n">
-        <v>0</v>
+      <c r="T51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U51" s="9" t="n">
         <v>0</v>
@@ -6007,8 +6007,8 @@
       <c r="Y51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z51" s="9" t="n">
-        <v>0</v>
+      <c r="Z51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA51" s="10" t="n">
         <v>1</v>
@@ -6281,7 +6281,7 @@
         </is>
       </c>
       <c r="P54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q54" s="9" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="P56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q56" s="9" t="n">
         <v>1</v>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6625,8 +6625,8 @@
       <c r="Y57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z57" s="9" t="n">
-        <v>0</v>
+      <c r="Z57" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA57" s="10" t="n">
         <v>1</v>
@@ -7008,7 +7008,7 @@
         </is>
       </c>
       <c r="P61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q61" s="9" t="n">
         <v>0</v>
@@ -7017,7 +7017,7 @@
         <v>0</v>
       </c>
       <c r="S61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61" s="9" t="n">
         <v>0</v>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7348,8 +7348,8 @@
       <c r="Y64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z64" s="9" t="n">
-        <v>0</v>
+      <c r="Z64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA64" s="10" t="n">
         <v>1</v>
@@ -7762,8 +7762,8 @@
       <c r="W68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X68" s="9" t="n">
-        <v>2</v>
+      <c r="X68" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y68" s="9" t="n">
         <v>0</v>
@@ -8469,7 +8469,7 @@
         <v>0</v>
       </c>
       <c r="Q75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" s="9" t="n">
         <v>0</v>
@@ -8595,7 +8595,7 @@
         <v>0</v>
       </c>
       <c r="X76" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y76" s="9" t="n">
         <v>0</v>
@@ -8841,7 +8841,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8911,8 +8911,8 @@
       <c r="Y79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z79" s="9" t="n">
-        <v>0</v>
+      <c r="Z79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA79" s="10" t="n">
         <v>1</v>
@@ -9661,7 +9661,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9731,8 +9731,8 @@
       <c r="Y87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" s="9" t="n">
-        <v>0</v>
+      <c r="Z87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA87" s="10" t="n">
         <v>1</v>
@@ -10069,7 +10069,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -10139,8 +10139,8 @@
       <c r="Y91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z91" s="9" t="n">
-        <v>0</v>
+      <c r="Z91" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA91" s="10" t="n">
         <v>1</v>
@@ -10170,7 +10170,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10234,14 +10234,14 @@
       <c r="W92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X92" s="9" t="n">
-        <v>2</v>
+      <c r="X92" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" s="9" t="n">
-        <v>0</v>
+      <c r="Z92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA92" s="10" t="n">
         <v>1</v>
@@ -10271,7 +10271,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10285,13 +10285,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>4</v>
       </c>
       <c r="W93" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X93" s="10" t="n">
         <v>4</v>
@@ -10341,8 +10341,8 @@
       <c r="Y93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z93" s="9" t="n">
-        <v>0</v>
+      <c r="Z93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA93" s="10" t="n">
         <v>1</v>
@@ -10643,7 +10643,7 @@
         <v>0</v>
       </c>
       <c r="X96" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y96" s="9" t="n">
         <v>0</v>
@@ -11210,13 +11210,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>4</v>
       </c>
       <c r="W102" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X102" s="10" t="n">
         <v>4</v>
@@ -11301,7 +11301,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11371,8 +11371,8 @@
       <c r="Y103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z103" s="9" t="n">
-        <v>0</v>
+      <c r="Z103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA103" s="10" t="n">
         <v>1</v>
@@ -11507,7 +11507,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11577,8 +11577,8 @@
       <c r="Y105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z105" s="9" t="n">
-        <v>0</v>
+      <c r="Z105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA105" s="10" t="n">
         <v>1</v>
@@ -11612,7 +11612,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -11664,8 +11664,8 @@
       <c r="S106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T106" s="9" t="n">
-        <v>0</v>
+      <c r="T106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U106" s="9" t="n">
         <v>0</v>
@@ -11682,8 +11682,8 @@
       <c r="Y106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" s="9" t="n">
-        <v>0</v>
+      <c r="Z106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA106" s="10" t="n">
         <v>1</v>
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12298,8 +12298,8 @@
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="9" t="n">
-        <v>0</v>
+      <c r="Z112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
@@ -12438,7 +12438,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12508,8 +12508,8 @@
       <c r="Y114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z114" s="9" t="n">
-        <v>0</v>
+      <c r="Z114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA114" s="10" t="n">
         <v>1</v>
@@ -12543,7 +12543,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12613,8 +12613,8 @@
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="9" t="n">
-        <v>0</v>
+      <c r="Z115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA115" s="10" t="n">
         <v>1</v>
@@ -12854,7 +12854,7 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12868,13 +12868,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>0</v>
       </c>
       <c r="V118" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
@@ -12924,8 +12924,8 @@
       <c r="Y118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z118" s="9" t="n">
-        <v>0</v>
+      <c r="Z118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA118" s="10" t="n">
         <v>1</v>
@@ -12955,7 +12955,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -13025,8 +13025,8 @@
       <c r="Y119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z119" s="9" t="n">
-        <v>0</v>
+      <c r="Z119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA119" s="10" t="n">
         <v>1</v>
@@ -13060,7 +13060,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -13130,8 +13130,8 @@
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z120" s="9" t="n">
-        <v>0</v>
+      <c r="Z120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA120" s="10" t="n">
         <v>1</v>
@@ -14096,7 +14096,7 @@
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -14166,8 +14166,8 @@
       <c r="Y130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z130" s="9" t="n">
-        <v>0</v>
+      <c r="Z130" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA130" s="10" t="n">
         <v>1</v>
@@ -14440,7 +14440,7 @@
         </is>
       </c>
       <c r="P133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q133" s="9" t="n">
         <v>0</v>
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -15284,8 +15284,8 @@
       <c r="R141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S141" s="9" t="n">
-        <v>1</v>
+      <c r="S141" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T141" s="9" t="n">
         <v>0</v>
@@ -15620,8 +15620,8 @@
       <c r="Y144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z144" s="9" t="n">
-        <v>0</v>
+      <c r="Z144" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA144" s="9" t="n">
         <v>0</v>
@@ -16337,7 +16337,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -16370,7 +16370,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -16403,7 +16403,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -16436,7 +16436,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -16469,7 +16469,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -16502,7 +16502,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -16535,7 +16535,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -16601,7 +16601,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -16634,7 +16634,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -16667,7 +16667,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -16733,7 +16733,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -16865,7 +16865,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -16931,7 +16931,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -16964,7 +16964,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -17030,7 +17030,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -17063,7 +17063,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -17096,7 +17096,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -17129,7 +17129,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -17162,7 +17162,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -17261,7 +17261,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -17327,7 +17327,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>

--- a/docs/d/109/inyear.xlsx
+++ b/docs/d/109/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/109/inyear.xlsx
+++ b/docs/d/109/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/109/inyear.xlsx
+++ b/docs/d/109/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/109/inyear.xlsx
+++ b/docs/d/109/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/109/inyear.xlsx
+++ b/docs/d/109/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 16 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 16 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 28 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 28 clubs short</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -1005,8 +1005,8 @@
       <c r="S3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T3" s="9" t="n">
-        <v>0</v>
+      <c r="T3" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U3" s="9" t="n">
         <v>0</v>
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-7</v>
+        <v>1</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>0</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W5" s="9" t="n">
         <v>0</v>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="P7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" s="9" t="n">
         <v>1</v>
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>2</v>
       </c>
       <c r="R14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" s="9" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="P16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="9" t="n">
         <v>0</v>
@@ -2425,13 +2425,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2530,13 +2530,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>4</v>
       </c>
       <c r="W19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" s="10" t="n">
         <v>6</v>
@@ -2732,13 +2732,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>4</v>
       </c>
       <c r="W25" s="10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X25" s="10" t="n">
         <v>5</v>
@@ -3459,13 +3459,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -3669,13 +3669,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>4</v>
       </c>
       <c r="W29" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X29" s="10" t="n">
         <v>7</v>
@@ -3760,7 +3760,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3774,13 +3774,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3818,8 +3818,8 @@
       <c r="U30" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="V30" s="9" t="n">
-        <v>2</v>
+      <c r="V30" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>0</v>
@@ -4291,13 +4291,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5224,17 +5224,17 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L44" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M44" s="8" t="n">
@@ -5268,8 +5268,8 @@
       <c r="U44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V44" s="9" t="n">
-        <v>3</v>
+      <c r="V44" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5329,17 +5329,17 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L45" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M45" s="8" t="n">
@@ -5377,7 +5377,7 @@
         <v>4</v>
       </c>
       <c r="W45" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X45" s="10" t="n">
         <v>4</v>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5667,7 +5667,7 @@
         </is>
       </c>
       <c r="P48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q48" s="9" t="n">
         <v>0</v>
@@ -5678,8 +5678,8 @@
       <c r="S48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T48" s="9" t="n">
-        <v>0</v>
+      <c r="T48" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U48" s="9" t="n">
         <v>0</v>
@@ -6281,7 +6281,7 @@
         </is>
       </c>
       <c r="P54" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q54" s="9" t="n">
         <v>0</v>
@@ -6345,7 +6345,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6388,8 +6388,8 @@
       <c r="P55" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q55" s="9" t="n">
-        <v>1</v>
+      <c r="Q55" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R55" s="9" t="n">
         <v>0</v>
@@ -6569,13 +6569,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>4</v>
       </c>
       <c r="W57" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X57" s="10" t="n">
         <v>4</v>
@@ -7185,13 +7185,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         </is>
       </c>
       <c r="P63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q63" s="9" t="n">
         <v>0</v>
@@ -7496,17 +7496,17 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>-25</v>
-      </c>
-      <c r="L66" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-22</v>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M66" s="8" t="n">
@@ -7544,7 +7544,7 @@
         <v>4</v>
       </c>
       <c r="W66" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X66" s="9" t="n">
         <v>0</v>
@@ -7916,13 +7916,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>-24</v>
+        <v>-10</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -9055,13 +9055,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -9090,8 +9090,8 @@
       <c r="R81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S81" s="9" t="n">
-        <v>1</v>
+      <c r="S81" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T81" s="9" t="n">
         <v>0</v>
@@ -9451,7 +9451,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9492,7 +9492,7 @@
         </is>
       </c>
       <c r="P85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q85" s="9" t="n">
         <v>0</v>
@@ -9500,8 +9500,8 @@
       <c r="R85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S85" s="9" t="n">
-        <v>1</v>
+      <c r="S85" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T85" s="9" t="n">
         <v>0</v>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="P90" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q90" s="9" t="n">
         <v>1</v>
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="P92" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q92" s="9" t="n">
         <v>0</v>
@@ -10382,13 +10382,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>4</v>
       </c>
       <c r="W94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X94" s="10" t="n">
         <v>4</v>
@@ -11303,13 +11303,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>44</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>-17</v>
+        <v>-11</v>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>4</v>
       </c>
       <c r="W103" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X103" s="10" t="n">
         <v>4</v>
@@ -11408,13 +11408,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>4</v>
       </c>
       <c r="W104" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X104" s="10" t="n">
         <v>4</v>
@@ -11925,13 +11925,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>56</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -12545,17 +12545,17 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-14</v>
-      </c>
-      <c r="L115" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-12</v>
+      </c>
+      <c r="L115" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M115" s="8" t="n">
@@ -12590,7 +12590,7 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -13787,13 +13787,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>0</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
@@ -14409,13 +14409,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>0</v>
       </c>
       <c r="V133" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W133" s="9" t="n">
         <v>0</v>
@@ -14611,13 +14611,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         </is>
       </c>
       <c r="P135" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q135" s="9" t="n">
         <v>0</v>
@@ -14647,7 +14647,7 @@
         <v>0</v>
       </c>
       <c r="S135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T135" s="9" t="n">
         <v>0</v>
@@ -15027,13 +15027,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
@@ -15132,13 +15132,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -15237,13 +15237,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>-13</v>
+        <v>-11</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -15342,13 +15342,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -15447,13 +15447,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -15552,13 +15552,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>-13</v>
+        <v>-10</v>
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
@@ -15599,8 +15599,8 @@
       <c r="V144" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W144" s="9" t="n">
-        <v>2</v>
+      <c r="W144" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X144" s="10" t="n">
         <v>7</v>
@@ -16174,13 +16174,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L150" s="7" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>0</v>
       </c>
       <c r="V150" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W150" s="9" t="n">
         <v>0</v>
@@ -16535,7 +16535,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -16700,7 +16700,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -16766,7 +16766,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -16781,7 +16781,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -16799,7 +16799,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -16814,7 +16814,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -16865,7 +16865,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -16979,7 +16979,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -17096,7 +17096,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -17129,7 +17129,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -17375,7 +17375,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -17558,7 +17558,7 @@
         <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>

--- a/docs/d/109/inyear.xlsx
+++ b/docs/d/109/inyear.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$152</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 16 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 16 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 28 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 28 clubs short</t>
         </is>
       </c>
     </row>
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>4</v>
       </c>
       <c r="W16" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X16" s="10" t="n">
         <v>7</v>
@@ -2411,7 +2411,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2425,13 +2425,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2469,8 +2469,8 @@
       <c r="U17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V17" s="9" t="n">
-        <v>3</v>
+      <c r="V17" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -3354,13 +3354,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3459,13 +3459,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>4</v>
       </c>
       <c r="W27" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X27" s="10" t="n">
         <v>6</v>
@@ -3825,7 +3825,7 @@
         <v>0</v>
       </c>
       <c r="X30" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y30" s="9" t="n">
         <v>0</v>
@@ -3929,8 +3929,8 @@
       <c r="W31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X31" s="9" t="n">
-        <v>0</v>
+      <c r="X31" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y31" s="9" t="n">
         <v>0</v>
@@ -5119,13 +5119,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5224,13 +5224,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5262,8 +5262,8 @@
       <c r="S44" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T44" s="9" t="n">
-        <v>0</v>
+      <c r="T44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U44" s="9" t="n">
         <v>0</v>
@@ -5434,13 +5434,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>4</v>
       </c>
       <c r="W48" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X48" s="10" t="n">
         <v>5</v>
@@ -6569,13 +6569,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6639,24 +6639,24 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>28679541</v>
+        <v>7068043</v>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Smyrna Toastmasters</t>
+          <t>Club der lebenden Worte</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6670,17 +6670,17 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M58" s="8" t="n">
@@ -6720,20 +6720,26 @@
       <c r="W58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X58" s="9" t="n">
-        <v>0</v>
+      <c r="X58" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z58" s="9" t="n">
-        <v>0</v>
+      <c r="Z58" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA58" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB58" s="4" t="n"/>
-      <c r="AC58" s="4" t="inlineStr"/>
+      <c r="AB58" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC58" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -6747,11 +6753,11 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>7068043</v>
+        <v>1027156</v>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Club der lebenden Worte</t>
+          <t>Rhetorik Klub Basel</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
@@ -6769,13 +6775,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6814,7 +6820,7 @@
         <v>0</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -6852,15 +6858,15 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1027156</v>
+        <v>28678472</v>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Rhetorik Klub Basel</t>
+          <t>Rosental Bilingual Basel Toastmasters Club</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6874,13 +6880,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6901,7 +6907,7 @@
         </is>
       </c>
       <c r="P60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q60" s="9" t="n">
         <v>0</v>
@@ -6910,10 +6916,10 @@
         <v>0</v>
       </c>
       <c r="S60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U60" s="9" t="n">
         <v>0</v>
@@ -6925,7 +6931,7 @@
         <v>0</v>
       </c>
       <c r="X60" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y60" s="9" t="n">
         <v>0</v>
@@ -6937,13 +6943,9 @@
         <v>1</v>
       </c>
       <c r="AB60" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC60" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -6957,11 +6959,11 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>28678472</v>
+        <v>2959165</v>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Rosental Bilingual Basel Toastmasters Club</t>
+          <t>Toastmasters Luzern</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
@@ -6979,17 +6981,17 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L61" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M61" s="8" t="n">
@@ -7017,20 +7019,20 @@
       <c r="S61" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T61" s="10" t="n">
-        <v>1</v>
+      <c r="T61" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V61" s="9" t="n">
-        <v>2</v>
+      <c r="V61" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X61" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y61" s="9" t="n">
         <v>0</v>
@@ -7042,9 +7044,13 @@
         <v>1</v>
       </c>
       <c r="AB61" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC61" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC61" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -7054,19 +7060,19 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>2959165</v>
+        <v>2495638</v>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Luzern</t>
+          <t>Basel Multilingual Toastmasters</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7080,17 +7086,17 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M62" s="8" t="n">
@@ -7116,7 +7122,7 @@
         <v>0</v>
       </c>
       <c r="S62" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T62" s="9" t="n">
         <v>0</v>
@@ -7124,11 +7130,11 @@
       <c r="U62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V62" s="10" t="n">
-        <v>4</v>
+      <c r="V62" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W62" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X62" s="10" t="n">
         <v>4</v>
@@ -7143,11 +7149,11 @@
         <v>1</v>
       </c>
       <c r="AB62" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC62" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -7163,15 +7169,15 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>2495638</v>
+        <v>28677990</v>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Basel Multilingual Toastmasters</t>
+          <t>Endress+Hauser Toastmasters</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7185,13 +7191,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>-7</v>
+        <v>-11</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7241,20 +7247,16 @@
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="10" t="n">
-        <v>1</v>
+      <c r="Z63" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA63" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB63" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC63" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -7268,15 +7270,15 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>28677990</v>
+        <v>4108355</v>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Endress+Hauser Toastmasters</t>
+          <t>Novartis Basel Toastmasters Club</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7290,17 +7292,17 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L64" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M64" s="8" t="n">
@@ -7325,17 +7327,17 @@
       <c r="R64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" s="9" t="n">
-        <v>0</v>
+      <c r="S64" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U64" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -7346,16 +7348,20 @@
       <c r="Y64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z64" s="9" t="n">
-        <v>0</v>
+      <c r="Z64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA64" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB64" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC64" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC64" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -7369,15 +7375,15 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>4108355</v>
+        <v>6597338</v>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Novartis Basel Toastmasters Club</t>
+          <t>RoBaToMaS - Roche Basel Toastmasters</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7391,13 +7397,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>-5</v>
+        <v>-22</v>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
@@ -7405,11 +7411,11 @@
         </is>
       </c>
       <c r="M65" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O65" s="7" t="inlineStr">
@@ -7418,7 +7424,7 @@
         </is>
       </c>
       <c r="P65" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q65" s="9" t="n">
         <v>0</v>
@@ -7426,39 +7432,39 @@
       <c r="R65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S65" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T65" s="10" t="n">
-        <v>1</v>
+      <c r="S65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V65" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W65" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X65" s="10" t="n">
+      <c r="V65" s="10" t="n">
         <v>4</v>
       </c>
+      <c r="W65" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="X65" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z65" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA65" s="10" t="n">
-        <v>1</v>
+      <c r="AA65" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB65" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC65" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -7470,15 +7476,15 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>6597338</v>
+        <v>2890562</v>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>RoBaToMaS - Roche Basel Toastmasters</t>
+          <t>Basel International Speakers</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
@@ -7496,25 +7502,25 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>-22</v>
-      </c>
-      <c r="L66" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M66" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O66" s="7" t="inlineStr">
@@ -7534,32 +7540,32 @@
       <c r="S66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T66" s="9" t="n">
-        <v>0</v>
+      <c r="T66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V66" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W66" s="10" t="n">
+      <c r="V66" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W66" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y66" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA66" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB66" s="4" t="n">
         <v>7</v>
-      </c>
-      <c r="X66" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y66" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z66" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA66" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB66" s="4" t="n">
-        <v>8</v>
       </c>
       <c r="AC66" s="4" t="inlineStr">
         <is>
@@ -7579,15 +7585,15 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>2890562</v>
+        <v>2825157</v>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Basel International Speakers</t>
+          <t>Innovative Speakers Allschwil</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7601,13 +7607,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7637,22 +7643,22 @@
         <v>0</v>
       </c>
       <c r="S67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T67" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U67" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X67" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y67" s="9" t="n">
         <v>0</v>
@@ -7664,11 +7670,11 @@
         <v>1</v>
       </c>
       <c r="AB67" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC67" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -7684,15 +7690,15 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>2825157</v>
+        <v>4459254</v>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Innovative Speakers Allschwil</t>
+          <t>Novartis Campus Speakers</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7706,17 +7712,17 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L68" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-11</v>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M68" s="8" t="n">
@@ -7732,26 +7738,26 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P68" s="9" t="n">
-        <v>0</v>
+      <c r="P68" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Q68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S68" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T68" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" s="9" t="n">
-        <v>0</v>
+      <c r="S68" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T68" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7789,15 +7795,15 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>4459254</v>
+        <v>5813</v>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Novartis Campus Speakers</t>
+          <t>Toastmasters of Basel</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7811,17 +7817,17 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M69" s="8" t="n">
@@ -7837,48 +7843,48 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P69" s="10" t="n">
+      <c r="P69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB69" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="Q69" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T69" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U69" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X69" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z69" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA69" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB69" s="4" t="n">
-        <v>10</v>
-      </c>
       <c r="AC69" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -7890,19 +7896,19 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>5813</v>
+        <v>3436</v>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters of Basel</t>
+          <t>Bern Toastmasters Club</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7916,13 +7922,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>-10</v>
+        <v>-18</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7946,13 +7952,13 @@
         <v>0</v>
       </c>
       <c r="Q70" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R70" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T70" s="9" t="n">
         <v>0</v>
@@ -7961,29 +7967,29 @@
         <v>0</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X70" s="9" t="n">
-        <v>1</v>
+      <c r="X70" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z70" s="9" t="n">
-        <v>0</v>
+      <c r="Z70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA70" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB70" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC70" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -7999,15 +8005,15 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>3436</v>
+        <v>6626588</v>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Bern Toastmasters Club</t>
+          <t>International Baden Toastmasters</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -8021,13 +8027,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>-18</v>
+        <v>-5</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -8047,11 +8053,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P71" s="9" t="n">
-        <v>0</v>
+      <c r="P71" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" s="9" t="n">
         <v>0</v>
@@ -8071,8 +8077,8 @@
       <c r="W71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X71" s="10" t="n">
-        <v>6</v>
+      <c r="X71" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y71" s="9" t="n">
         <v>0</v>
@@ -8104,15 +8110,15 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>6626588</v>
+        <v>28679975</v>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>International Baden Toastmasters</t>
+          <t>Reinach Toastmasters Club</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8126,17 +8132,17 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L72" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M72" s="8" t="n">
@@ -8152,17 +8158,17 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P72" s="10" t="n">
-        <v>4</v>
+      <c r="P72" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Q72" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S72" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T72" s="9" t="n">
         <v>0</v>
@@ -8171,31 +8177,27 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W72" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y72" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z72" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA72" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB72" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W72" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X72" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y72" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z72" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA72" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB72" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC72" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+      <c r="AC72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -8209,15 +8211,15 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>28679975</v>
+        <v>28678828</v>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Reinach Toastmasters Club</t>
+          <t>Roche Rotkreuz AVR Toastmasters Club</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8231,13 +8233,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
@@ -8245,11 +8247,11 @@
         </is>
       </c>
       <c r="M73" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O73" s="7" t="inlineStr">
@@ -8258,7 +8260,7 @@
         </is>
       </c>
       <c r="P73" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q73" s="9" t="n">
         <v>0</v>
@@ -8281,8 +8283,8 @@
       <c r="W73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X73" s="10" t="n">
-        <v>7</v>
+      <c r="X73" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y73" s="9" t="n">
         <v>0</v>
@@ -8290,8 +8292,8 @@
       <c r="Z73" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA73" s="10" t="n">
-        <v>1</v>
+      <c r="AA73" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB73" s="4" t="n">
         <v>2</v>
@@ -8301,24 +8303,24 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>28678828</v>
+        <v>5048</v>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Roche Rotkreuz AVR Toastmasters Club</t>
+          <t>International Geneva Toastmasters Club</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8332,13 +8334,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
@@ -8346,11 +8348,11 @@
         </is>
       </c>
       <c r="M74" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O74" s="7" t="inlineStr">
@@ -8359,7 +8361,7 @@
         </is>
       </c>
       <c r="P74" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q74" s="9" t="n">
         <v>0</v>
@@ -8368,7 +8370,7 @@
         <v>0</v>
       </c>
       <c r="S74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T74" s="9" t="n">
         <v>0</v>
@@ -8376,14 +8378,14 @@
       <c r="U74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V74" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W74" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X74" s="9" t="n">
-        <v>1</v>
+      <c r="V74" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W74" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="X74" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y74" s="9" t="n">
         <v>0</v>
@@ -8391,13 +8393,17 @@
       <c r="Z74" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA74" s="9" t="n">
-        <v>0</v>
+      <c r="AA74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB74" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC74" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC74" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -8411,11 +8417,11 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>5048</v>
+        <v>2528283</v>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>International Geneva Toastmasters Club</t>
+          <t>International Toastmasters Club of Nyon</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
@@ -8433,13 +8439,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>4</v>
+        <v>-8</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -8460,19 +8466,19 @@
         </is>
       </c>
       <c r="P75" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S75" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T75" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="T75" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U75" s="9" t="n">
         <v>0</v>
@@ -8480,11 +8486,11 @@
       <c r="V75" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W75" s="10" t="n">
-        <v>4</v>
+      <c r="W75" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X75" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y75" s="9" t="n">
         <v>0</v>
@@ -8496,11 +8502,11 @@
         <v>1</v>
       </c>
       <c r="AB75" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC75" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -8516,15 +8522,15 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>2528283</v>
+        <v>28675698</v>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>International Toastmasters Club of Nyon</t>
+          <t>P&amp;G Geneva Toastmasters</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8538,17 +8544,17 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L76" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L76" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M76" s="8" t="n">
@@ -8565,10 +8571,10 @@
         </is>
       </c>
       <c r="P76" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q76" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R76" s="9" t="n">
         <v>0</v>
@@ -8576,14 +8582,14 @@
       <c r="S76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T76" s="10" t="n">
-        <v>1</v>
+      <c r="T76" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V76" s="10" t="n">
-        <v>4</v>
+      <c r="V76" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8601,7 +8607,7 @@
         <v>1</v>
       </c>
       <c r="AB76" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC76" s="4" t="inlineStr">
         <is>
@@ -8621,15 +8627,15 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>28675698</v>
+        <v>1153360</v>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>P&amp;G Geneva Toastmasters</t>
+          <t>UN Geneva Toastmasters</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8643,17 +8649,17 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L77" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L77" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M77" s="8" t="n">
@@ -8681,20 +8687,20 @@
       <c r="S77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U77" s="9" t="n">
-        <v>0</v>
+      <c r="T77" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V77" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X77" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y77" s="9" t="n">
         <v>0</v>
@@ -8706,11 +8712,11 @@
         <v>1</v>
       </c>
       <c r="AB77" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC77" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -8722,19 +8728,19 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>1153360</v>
+        <v>28678634</v>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>UN Geneva Toastmasters</t>
+          <t>AWSome Geneva Toastmaster</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8748,17 +8754,17 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M78" s="8" t="n">
@@ -8786,11 +8792,11 @@
       <c r="S78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T78" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U78" s="10" t="n">
-        <v>2</v>
+      <c r="T78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V78" s="9" t="n">
         <v>3</v>
@@ -8811,13 +8817,9 @@
         <v>1</v>
       </c>
       <c r="AB78" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC78" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -8831,11 +8833,11 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>28678634</v>
+        <v>6972006</v>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>AWSome Geneva Toastmaster</t>
+          <t>Caterpillar Toastmaster Club Geneva</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
@@ -8853,10 +8855,10 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K79" s="4" t="n">
         <v>-2</v>
@@ -8898,13 +8900,13 @@
         <v>0</v>
       </c>
       <c r="V79" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X79" s="10" t="n">
-        <v>4</v>
+      <c r="X79" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y79" s="9" t="n">
         <v>0</v>
@@ -8932,15 +8934,15 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>6972006</v>
+        <v>5896838</v>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Caterpillar Toastmaster Club Geneva</t>
+          <t>Impact Toastmasters Geneva</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8954,13 +8956,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8981,16 +8983,16 @@
         </is>
       </c>
       <c r="P80" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S80" s="9" t="n">
-        <v>0</v>
+      <c r="S80" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T80" s="9" t="n">
         <v>0</v>
@@ -8999,13 +9001,13 @@
         <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X80" s="9" t="n">
-        <v>0</v>
+      <c r="X80" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y80" s="9" t="n">
         <v>0</v>
@@ -9017,9 +9019,13 @@
         <v>1</v>
       </c>
       <c r="AB80" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC80" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC80" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -9033,11 +9039,11 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>5896838</v>
+        <v>1527955</v>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Impact Toastmasters Geneva</t>
+          <t>Verbissimo</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
@@ -9055,13 +9061,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -9082,16 +9088,16 @@
         </is>
       </c>
       <c r="P81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q81" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S81" s="10" t="n">
-        <v>2</v>
+      <c r="S81" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T81" s="9" t="n">
         <v>0</v>
@@ -9099,14 +9105,14 @@
       <c r="U81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V81" s="9" t="n">
-        <v>3</v>
+      <c r="V81" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W81" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X81" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y81" s="9" t="n">
         <v>0</v>
@@ -9118,11 +9124,11 @@
         <v>1</v>
       </c>
       <c r="AB81" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC81" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -9134,19 +9140,19 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>1527955</v>
+        <v>28680175</v>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Verbissimo</t>
+          <t>Embajadores del Español TM</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9160,17 +9166,17 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L82" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M82" s="8" t="n">
@@ -9187,7 +9193,7 @@
         </is>
       </c>
       <c r="P82" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q82" s="9" t="n">
         <v>0</v>
@@ -9204,32 +9210,26 @@
       <c r="U82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V82" s="10" t="n">
-        <v>4</v>
+      <c r="V82" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X82" s="10" t="n">
-        <v>5</v>
+      <c r="X82" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="10" t="n">
-        <v>1</v>
+      <c r="Z82" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB82" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC82" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AB82" s="4" t="n"/>
+      <c r="AC82" s="4" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -9243,15 +9243,15 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>28680175</v>
+        <v>28675805</v>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Embajadores del Español TM</t>
+          <t>Insights Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -9265,17 +9265,17 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M83" s="8" t="n">
@@ -9303,31 +9303,33 @@
       <c r="S83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T83" s="9" t="n">
-        <v>0</v>
+      <c r="T83" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X83" s="9" t="n">
-        <v>0</v>
+      <c r="X83" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z83" s="9" t="n">
-        <v>0</v>
+      <c r="Z83" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA83" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB83" s="4" t="n"/>
+      <c r="AB83" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="AC83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
@@ -9342,15 +9344,15 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>28675805</v>
+        <v>6634</v>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Insights Advanced Toastmasters Club</t>
+          <t>Lausanne International Club</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9364,17 +9366,17 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L84" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L84" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M84" s="8" t="n">
@@ -9391,7 +9393,7 @@
         </is>
       </c>
       <c r="P84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q84" s="9" t="n">
         <v>0</v>
@@ -9399,23 +9401,23 @@
       <c r="R84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S84" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T84" s="10" t="n">
-        <v>1</v>
+      <c r="S84" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T84" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V84" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W84" s="9" t="n">
-        <v>0</v>
+      <c r="V84" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W84" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="X84" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y84" s="9" t="n">
         <v>0</v>
@@ -9427,9 +9429,13 @@
         <v>1</v>
       </c>
       <c r="AB84" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC84" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC84" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -9443,15 +9449,15 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>6634</v>
+        <v>1498284</v>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Lausanne International Club</t>
+          <t>Nespeakers</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9465,25 +9471,25 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L85" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L85" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M85" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N85" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O85" s="7" t="inlineStr">
@@ -9492,7 +9498,7 @@
         </is>
       </c>
       <c r="P85" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q85" s="9" t="n">
         <v>0</v>
@@ -9500,8 +9506,8 @@
       <c r="R85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S85" s="10" t="n">
-        <v>2</v>
+      <c r="S85" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T85" s="9" t="n">
         <v>0</v>
@@ -9509,32 +9515,28 @@
       <c r="U85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V85" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W85" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X85" s="10" t="n">
-        <v>4</v>
+      <c r="V85" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W85" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X85" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z85" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA85" s="10" t="n">
-        <v>1</v>
+      <c r="Z85" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB85" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC85" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -9548,11 +9550,11 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>1498284</v>
+        <v>6901411</v>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Nespeakers</t>
+          <t>Richemont Toastmasters Club</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
@@ -9570,13 +9572,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9621,19 +9623,19 @@
         <v>0</v>
       </c>
       <c r="X86" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" s="9" t="n">
-        <v>0</v>
+      <c r="Z86" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="AA86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AB86" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC86" s="4" t="inlineStr"/>
     </row>
@@ -9649,11 +9651,11 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>6901411</v>
+        <v>28680492</v>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Richemont Toastmasters Club</t>
+          <t>Toastmasters Swissquote Club</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
@@ -9671,25 +9673,25 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K87" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L87" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L87" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M87" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O87" s="7" t="inlineStr">
@@ -9727,11 +9729,11 @@
       <c r="Y87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA87" s="9" t="n">
-        <v>0</v>
+      <c r="Z87" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB87" s="4" t="n">
         <v>1</v>
@@ -9746,19 +9748,19 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>28680492</v>
+        <v>28679960</v>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Swissquote Club</t>
+          <t>Alianza Eucan Toastmasters Club</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9775,10 +9777,10 @@
         <v>20</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
@@ -9823,13 +9825,13 @@
         <v>0</v>
       </c>
       <c r="X88" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z88" s="9" t="n">
-        <v>0</v>
+      <c r="Z88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA88" s="10" t="n">
         <v>1</v>
@@ -9851,11 +9853,11 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>28679960</v>
+        <v>28677321</v>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Alianza Eucan Toastmasters Club</t>
+          <t>BMS Boudry Toastmasters</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
@@ -9873,13 +9875,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -9900,10 +9902,10 @@
         </is>
       </c>
       <c r="P89" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R89" s="9" t="n">
         <v>0</v>
@@ -9924,7 +9926,7 @@
         <v>0</v>
       </c>
       <c r="X89" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y89" s="9" t="n">
         <v>0</v>
@@ -9936,7 +9938,7 @@
         <v>1</v>
       </c>
       <c r="AB89" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC89" s="4" t="inlineStr"/>
     </row>
@@ -9952,15 +9954,15 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>28677321</v>
+        <v>28678356</v>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>BMS Boudry Toastmasters</t>
+          <t>Helvetica Advanced Speakers</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9974,17 +9976,17 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L90" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L90" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M90" s="8" t="n">
@@ -10001,43 +10003,43 @@
         </is>
       </c>
       <c r="P90" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W90" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X90" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y90" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z90" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA90" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB90" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="Q90" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X90" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z90" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA90" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB90" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="AC90" s="4" t="inlineStr"/>
     </row>
@@ -10053,15 +10055,15 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>28678356</v>
+        <v>5507222</v>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Helvetica Advanced Speakers</t>
+          <t>Neuchatel Toastmasters</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -10075,17 +10077,17 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L91" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-9</v>
+      </c>
+      <c r="L91" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M91" s="8" t="n">
@@ -10102,7 +10104,7 @@
         </is>
       </c>
       <c r="P91" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q91" s="9" t="n">
         <v>0</v>
@@ -10110,8 +10112,8 @@
       <c r="R91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S91" s="9" t="n">
-        <v>0</v>
+      <c r="S91" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T91" s="9" t="n">
         <v>0</v>
@@ -10120,45 +10122,49 @@
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X91" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z91" s="9" t="n">
-        <v>0</v>
+      <c r="Z91" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA91" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB91" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC91" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC91" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>5507222</v>
+        <v>1343922</v>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Neuchatel Toastmasters</t>
+          <t>UBS Rhetoric Club CH</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
@@ -10176,17 +10182,17 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M92" s="8" t="n">
@@ -10203,49 +10209,45 @@
         </is>
       </c>
       <c r="P92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X92" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA92" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB92" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="Q92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S92" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V92" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X92" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z92" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA92" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB92" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC92" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AC92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -10259,11 +10261,11 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>1343922</v>
+        <v>7945783</v>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>UBS Rhetoric Club CH</t>
+          <t>WintiSpeakers - Toastmasters Club Winterthur</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
@@ -10281,17 +10283,17 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L93" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L93" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M93" s="8" t="n">
@@ -10311,7 +10313,7 @@
         <v>0</v>
       </c>
       <c r="Q93" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R93" s="9" t="n">
         <v>0</v>
@@ -10329,7 +10331,7 @@
         <v>4</v>
       </c>
       <c r="W93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X93" s="10" t="n">
         <v>4</v>
@@ -10344,7 +10346,7 @@
         <v>1</v>
       </c>
       <c r="AB93" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC93" s="4" t="inlineStr"/>
     </row>
@@ -10360,11 +10362,11 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>7945783</v>
+        <v>3906</v>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>WintiSpeakers - Toastmasters Club Winterthur</t>
+          <t>Zurich Club</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
@@ -10382,13 +10384,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
@@ -10409,7 +10411,7 @@
         </is>
       </c>
       <c r="P94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q94" s="9" t="n">
         <v>0</v>
@@ -10430,7 +10432,7 @@
         <v>4</v>
       </c>
       <c r="W94" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X94" s="10" t="n">
         <v>4</v>
@@ -10445,9 +10447,13 @@
         <v>1</v>
       </c>
       <c r="AB94" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC94" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC94" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -10461,15 +10467,15 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>3906</v>
+        <v>7079280</v>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Zurich Club</t>
+          <t>Zurich Swiss Re Toastmasters</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10483,17 +10489,17 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L95" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M95" s="8" t="n">
@@ -10510,10 +10516,10 @@
         </is>
       </c>
       <c r="P95" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R95" s="9" t="n">
         <v>0</v>
@@ -10527,32 +10533,28 @@
       <c r="U95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V95" s="10" t="n">
-        <v>4</v>
+      <c r="V95" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W95" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="X95" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="X95" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="10" t="n">
-        <v>1</v>
+      <c r="Z95" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB95" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC95" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -10562,15 +10564,15 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>7079280</v>
+        <v>28676150</v>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Zurich Swiss Re Toastmasters</t>
+          <t>Ignite CH Toastmaster Leadership Circle</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
@@ -10588,13 +10590,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10602,11 +10604,11 @@
         </is>
       </c>
       <c r="M96" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N96" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O96" s="7" t="inlineStr">
@@ -10615,26 +10617,26 @@
         </is>
       </c>
       <c r="P96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q96" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V96" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
       </c>
@@ -10647,11 +10649,11 @@
       <c r="Z96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA96" s="10" t="n">
-        <v>1</v>
+      <c r="AA96" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB96" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC96" s="4" t="inlineStr"/>
     </row>
@@ -10667,11 +10669,11 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>28676150</v>
+        <v>5702915</v>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Ignite CH Toastmaster Leadership Circle</t>
+          <t>International Lunchtime Toastmasters - ILTM</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
@@ -10689,13 +10691,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10703,11 +10705,11 @@
         </is>
       </c>
       <c r="M97" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N97" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O97" s="7" t="inlineStr">
@@ -10740,7 +10742,7 @@
         <v>0</v>
       </c>
       <c r="X97" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y97" s="9" t="n">
         <v>0</v>
@@ -10748,8 +10750,8 @@
       <c r="Z97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA97" s="9" t="n">
-        <v>0</v>
+      <c r="AA97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB97" s="4" t="n">
         <v>3</v>
@@ -10768,11 +10770,11 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>5702915</v>
+        <v>28678816</v>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>International Lunchtime Toastmasters - ILTM</t>
+          <t>Public Speaking Club @ SIX</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
@@ -10790,13 +10792,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10841,7 +10843,7 @@
         <v>0</v>
       </c>
       <c r="X98" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y98" s="9" t="n">
         <v>0</v>
@@ -10853,7 +10855,7 @@
         <v>1</v>
       </c>
       <c r="AB98" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC98" s="4" t="inlineStr"/>
     </row>
@@ -10869,15 +10871,15 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>28678816</v>
+        <v>4156916</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Public Speaking Club @ SIX</t>
+          <t>Top Notch Toastmasters Zurich</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10891,17 +10893,17 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-10</v>
+      </c>
+      <c r="L99" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M99" s="8" t="n">
@@ -10929,34 +10931,38 @@
       <c r="S99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V99" s="9" t="n">
-        <v>0</v>
+      <c r="T99" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U99" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V99" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X99" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="X99" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z99" s="9" t="n">
-        <v>0</v>
+      <c r="Z99" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA99" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB99" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC99" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC99" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -10970,15 +10976,15 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>4156916</v>
+        <v>5611978</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Top Notch Toastmasters Zurich</t>
+          <t>UBS Rhetoric Club Opfikon</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10992,17 +10998,17 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L100" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L100" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M100" s="8" t="n">
@@ -11030,11 +11036,11 @@
       <c r="S100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T100" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U100" s="10" t="n">
-        <v>2</v>
+      <c r="T100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V100" s="10" t="n">
         <v>4</v>
@@ -11043,7 +11049,7 @@
         <v>1</v>
       </c>
       <c r="X100" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y100" s="9" t="n">
         <v>0</v>
@@ -11055,13 +11061,9 @@
         <v>1</v>
       </c>
       <c r="AB100" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC100" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC100" s="4" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -11071,19 +11073,19 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>5611978</v>
+        <v>1833930</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>UBS Rhetoric Club Opfikon</t>
+          <t>Rhetorik Club Winterthur</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11097,17 +11099,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L101" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-9</v>
+      </c>
+      <c r="L101" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M101" s="8" t="n">
@@ -11124,7 +11126,7 @@
         </is>
       </c>
       <c r="P101" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q101" s="9" t="n">
         <v>0</v>
@@ -11141,14 +11143,14 @@
       <c r="U101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V101" s="10" t="n">
-        <v>4</v>
+      <c r="V101" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W101" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X101" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y101" s="9" t="n">
         <v>0</v>
@@ -11160,9 +11162,13 @@
         <v>1</v>
       </c>
       <c r="AB101" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC101" s="4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AC101" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -11176,15 +11182,15 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>1833930</v>
+        <v>851701</v>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Rhetorik Club Winterthur</t>
+          <t>Rhetorik Club Zürich</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -11198,13 +11204,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>44</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
@@ -11225,43 +11231,43 @@
         </is>
       </c>
       <c r="P102" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q102" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W102" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V102" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W102" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="X102" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA102" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB102" s="4" t="n">
         <v>5</v>
-      </c>
-      <c r="Y102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z102" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA102" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB102" s="4" t="n">
-        <v>6</v>
       </c>
       <c r="AC102" s="4" t="inlineStr">
         <is>
@@ -11281,35 +11287,35 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>851701</v>
+        <v>587599</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Rhetorik Club Zürich</t>
+          <t>Turicum Toastmasters</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F103" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I103" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="J103" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="K103" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="F103" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G103" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H103" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I103" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="J103" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="K103" s="4" t="n">
-        <v>-11</v>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
@@ -11333,13 +11339,13 @@
         <v>1</v>
       </c>
       <c r="Q103" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R103" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T103" s="9" t="n">
         <v>0</v>
@@ -11350,8 +11356,8 @@
       <c r="V103" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W103" s="9" t="n">
-        <v>2</v>
+      <c r="W103" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="X103" s="10" t="n">
         <v>4</v>
@@ -11366,11 +11372,11 @@
         <v>1</v>
       </c>
       <c r="AB103" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC103" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -11386,15 +11392,15 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>587599</v>
+        <v>7058810</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Turicum Toastmasters</t>
+          <t>UBS Rhetoric Club Zurich City</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11408,17 +11414,17 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L104" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L104" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M104" s="8" t="n">
@@ -11438,13 +11444,13 @@
         <v>1</v>
       </c>
       <c r="Q104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R104" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S104" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T104" s="9" t="n">
         <v>0</v>
@@ -11455,8 +11461,8 @@
       <c r="V104" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W104" s="10" t="n">
-        <v>8</v>
+      <c r="W104" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X104" s="10" t="n">
         <v>4</v>
@@ -11471,13 +11477,9 @@
         <v>1</v>
       </c>
       <c r="AB104" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC104" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC104" s="4" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -11487,19 +11489,19 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>7058810</v>
+        <v>2904427</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>UBS Rhetoric Club Zurich City</t>
+          <t>Toastmasters St. Gallen</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11513,13 +11515,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -11540,10 +11542,10 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q105" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R105" s="9" t="n">
         <v>0</v>
@@ -11557,14 +11559,14 @@
       <c r="U105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V105" s="10" t="n">
-        <v>4</v>
+      <c r="V105" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X105" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y105" s="9" t="n">
         <v>0</v>
@@ -11576,9 +11578,13 @@
         <v>1</v>
       </c>
       <c r="AB105" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC105" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC105" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -11592,11 +11598,11 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>2904427</v>
+        <v>6962824</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters St. Gallen</t>
+          <t>UBS Speaks</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
@@ -11614,17 +11620,17 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L106" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L106" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M106" s="8" t="n">
@@ -11641,7 +11647,7 @@
         </is>
       </c>
       <c r="P106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q106" s="9" t="n">
         <v>0</v>
@@ -11659,7 +11665,7 @@
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
@@ -11677,11 +11683,11 @@
         <v>1</v>
       </c>
       <c r="AB106" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC106" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -11697,15 +11703,15 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>6962824</v>
+        <v>2600747</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>UBS Speaks</t>
+          <t>Walk The Talk Zurich Toastmasters</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11719,17 +11725,17 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L107" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L107" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M107" s="8" t="n">
@@ -11746,10 +11752,10 @@
         </is>
       </c>
       <c r="P107" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R107" s="9" t="n">
         <v>0</v>
@@ -11757,8 +11763,8 @@
       <c r="S107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T107" s="9" t="n">
-        <v>0</v>
+      <c r="T107" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U107" s="9" t="n">
         <v>0</v>
@@ -11770,7 +11776,7 @@
         <v>0</v>
       </c>
       <c r="X107" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y107" s="9" t="n">
         <v>0</v>
@@ -11782,13 +11788,9 @@
         <v>1</v>
       </c>
       <c r="AB107" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC107" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC107" s="4" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -11802,15 +11804,15 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>2600747</v>
+        <v>856858</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Walk The Talk Zurich Toastmasters</t>
+          <t>Zuriberg Toastmasters Club</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11824,17 +11826,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L108" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-4</v>
+      </c>
+      <c r="L108" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M108" s="8" t="n">
@@ -11851,7 +11853,7 @@
         </is>
       </c>
       <c r="P108" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q108" s="9" t="n">
         <v>1</v>
@@ -11860,10 +11862,10 @@
         <v>0</v>
       </c>
       <c r="S108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T108" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T108" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U108" s="9" t="n">
         <v>0</v>
@@ -11875,7 +11877,7 @@
         <v>0</v>
       </c>
       <c r="X108" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y108" s="9" t="n">
         <v>0</v>
@@ -11887,9 +11889,13 @@
         <v>1</v>
       </c>
       <c r="AB108" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC108" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC108" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -11899,15 +11905,15 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>856858</v>
+        <v>1167343</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Zuriberg Toastmasters Club</t>
+          <t>Horgen Talk'n'Heads Toastmasters Club</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
@@ -11925,17 +11931,17 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L109" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L109" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M109" s="8" t="n">
@@ -11952,16 +11958,16 @@
         </is>
       </c>
       <c r="P109" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q109" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S109" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T109" s="9" t="n">
         <v>0</v>
@@ -11970,13 +11976,13 @@
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X109" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y109" s="9" t="n">
         <v>0</v>
@@ -11988,11 +11994,11 @@
         <v>1</v>
       </c>
       <c r="AB109" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC109" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -12008,15 +12014,15 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>1167343</v>
+        <v>28679269</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Horgen Talk'n'Heads Toastmasters Club</t>
+          <t>Spotlight Toastmasters Club</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -12030,17 +12036,17 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L110" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L110" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M110" s="8" t="n">
@@ -12080,26 +12086,20 @@
       <c r="W110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X110" s="10" t="n">
-        <v>4</v>
+      <c r="X110" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z110" s="10" t="n">
-        <v>1</v>
+      <c r="Z110" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA110" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB110" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC110" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AB110" s="4" t="n"/>
+      <c r="AC110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -12113,15 +12113,15 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>28679269</v>
+        <v>7332</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Spotlight Toastmasters Club</t>
+          <t>TM International Club Zug Club</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12135,13 +12135,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         <v>0</v>
       </c>
       <c r="Q111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R111" s="9" t="n">
         <v>0</v>
@@ -12173,32 +12173,38 @@
       <c r="S111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T111" s="9" t="n">
-        <v>0</v>
+      <c r="T111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X111" s="9" t="n">
-        <v>1</v>
+      <c r="V111" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W111" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="X111" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="9" t="n">
-        <v>0</v>
+      <c r="Z111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA111" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB111" s="4" t="n"/>
-      <c r="AC111" s="4" t="inlineStr"/>
+      <c r="AB111" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC111" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -12212,15 +12218,15 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>7332</v>
+        <v>5850907</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>TM International Club Zug Club</t>
+          <t>Toastmasters@Deloitte</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12234,25 +12240,25 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L112" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L112" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M112" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N112" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O112" s="7" t="inlineStr">
@@ -12264,7 +12270,7 @@
         <v>0</v>
       </c>
       <c r="Q112" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R112" s="9" t="n">
         <v>0</v>
@@ -12272,38 +12278,34 @@
       <c r="S112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T112" s="10" t="n">
-        <v>1</v>
+      <c r="T112" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V112" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W112" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="X112" s="10" t="n">
-        <v>5</v>
+      <c r="V112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X112" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA112" s="10" t="n">
-        <v>1</v>
+      <c r="Z112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA112" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB112" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC112" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC112" s="4" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -12317,15 +12319,15 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>5850907</v>
+        <v>7091691</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters@Deloitte</t>
+          <t>UBS Toastmasters Europaallee</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12339,13 +12341,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -12353,11 +12355,11 @@
         </is>
       </c>
       <c r="M113" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N113" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O113" s="7" t="inlineStr">
@@ -12369,7 +12371,7 @@
         <v>0</v>
       </c>
       <c r="Q113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R113" s="9" t="n">
         <v>0</v>
@@ -12389,40 +12391,44 @@
       <c r="W113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X113" s="9" t="n">
-        <v>0</v>
+      <c r="X113" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z113" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA113" s="9" t="n">
-        <v>0</v>
+      <c r="Z113" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB113" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC113" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC113" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>7091691</v>
+        <v>6955832</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>UBS Toastmasters Europaallee</t>
+          <t>Blue Danube Leaders</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
@@ -12440,17 +12446,17 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L114" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-12</v>
+      </c>
+      <c r="L114" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M114" s="8" t="n">
@@ -12467,7 +12473,7 @@
         </is>
       </c>
       <c r="P114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q114" s="9" t="n">
         <v>0</v>
@@ -12485,13 +12491,13 @@
         <v>0</v>
       </c>
       <c r="V114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X114" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y114" s="9" t="n">
         <v>0</v>
@@ -12503,11 +12509,11 @@
         <v>1</v>
       </c>
       <c r="AB114" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC114" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -12523,15 +12529,15 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>6955832</v>
+        <v>6390</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Blue Danube Leaders</t>
+          <t>V.I.C. Toastmasters Club</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12548,10 +12554,10 @@
         <v>21</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-12</v>
+        <v>-6</v>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
@@ -12572,7 +12578,7 @@
         </is>
       </c>
       <c r="P115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q115" s="9" t="n">
         <v>0</v>
@@ -12583,20 +12589,20 @@
       <c r="S115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T115" s="9" t="n">
-        <v>0</v>
+      <c r="T115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V115" s="9" t="n">
-        <v>1</v>
+      <c r="V115" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W115" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X115" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y115" s="9" t="n">
         <v>0</v>
@@ -12608,11 +12614,11 @@
         <v>1</v>
       </c>
       <c r="AB115" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC115" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -12628,15 +12634,15 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>6390</v>
+        <v>1174718</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>V.I.C. Toastmasters Club</t>
+          <t>Vienna Speakers Club</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12653,10 +12659,10 @@
         <v>18</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>-9</v>
+        <v>-15</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12677,7 +12683,7 @@
         </is>
       </c>
       <c r="P116" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q116" s="9" t="n">
         <v>0</v>
@@ -12688,20 +12694,20 @@
       <c r="S116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T116" s="10" t="n">
-        <v>1</v>
+      <c r="T116" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V116" s="10" t="n">
-        <v>4</v>
+      <c r="V116" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W116" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X116" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
@@ -12713,11 +12719,11 @@
         <v>1</v>
       </c>
       <c r="AB116" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC116" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -12733,15 +12739,15 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>1174718</v>
+        <v>551</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Vienna Speakers Club</t>
+          <t>Vienna Toastmasters Club</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12755,17 +12761,17 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-15</v>
-      </c>
-      <c r="L117" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-23</v>
+      </c>
+      <c r="L117" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M117" s="8" t="n">
@@ -12785,7 +12791,7 @@
         <v>0</v>
       </c>
       <c r="Q117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R117" s="9" t="n">
         <v>0</v>
@@ -12799,14 +12805,14 @@
       <c r="U117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V117" s="9" t="n">
-        <v>0</v>
+      <c r="V117" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X117" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y117" s="9" t="n">
         <v>0</v>
@@ -12818,11 +12824,11 @@
         <v>1</v>
       </c>
       <c r="AB117" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC117" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -12834,19 +12840,19 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>551</v>
+        <v>28678311</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Vienna Toastmasters Club</t>
+          <t>After Work Speakers</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12860,17 +12866,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-23</v>
-      </c>
-      <c r="L118" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L118" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M118" s="8" t="n">
@@ -12890,7 +12896,7 @@
         <v>0</v>
       </c>
       <c r="Q118" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R118" s="9" t="n">
         <v>0</v>
@@ -12904,11 +12910,11 @@
       <c r="U118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V118" s="10" t="n">
-        <v>4</v>
+      <c r="V118" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W118" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X118" s="10" t="n">
         <v>5</v>
@@ -12923,13 +12929,9 @@
         <v>1</v>
       </c>
       <c r="AB118" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC118" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="AC118" s="4" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -12943,11 +12945,11 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>28678311</v>
+        <v>2869957</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>After Work Speakers</t>
+          <t>Blue Danube Speakers</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
@@ -12965,13 +12967,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>-2</v>
+        <v>-9</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -13010,13 +13012,13 @@
         <v>0</v>
       </c>
       <c r="V119" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X119" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y119" s="9" t="n">
         <v>0</v>
@@ -13028,7 +13030,7 @@
         <v>1</v>
       </c>
       <c r="AB119" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC119" s="4" t="inlineStr"/>
     </row>
@@ -13044,11 +13046,11 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>2869957</v>
+        <v>4502690</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Blue Danube Speakers</t>
+          <t>Rhetorikclub Toastmasters Salzburg</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
@@ -13066,13 +13068,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -13111,13 +13113,13 @@
         <v>0</v>
       </c>
       <c r="V120" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X120" s="10" t="n">
-        <v>4</v>
+      <c r="X120" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
@@ -13129,9 +13131,13 @@
         <v>1</v>
       </c>
       <c r="AB120" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC120" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC120" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -13145,11 +13151,11 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>4502690</v>
+        <v>5760999</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Rhetorikclub Toastmasters Salzburg</t>
+          <t>Toastmasters Rhetorikclub Innsbruck</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
@@ -13167,13 +13173,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>-6</v>
+        <v>-12</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -13212,13 +13218,13 @@
         <v>0</v>
       </c>
       <c r="V121" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X121" s="9" t="n">
-        <v>1</v>
+      <c r="X121" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y121" s="9" t="n">
         <v>0</v>
@@ -13230,7 +13236,7 @@
         <v>1</v>
       </c>
       <c r="AB121" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC121" s="4" t="inlineStr">
         <is>
@@ -13246,15 +13252,15 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>5760999</v>
+        <v>7873070</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Rhetorikclub Innsbruck</t>
+          <t>NIL Master Talk Toastmasters Club</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
@@ -13272,13 +13278,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-12</v>
+        <v>-5</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -13286,11 +13292,11 @@
         </is>
       </c>
       <c r="M122" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N122" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O122" s="7" t="inlineStr">
@@ -13316,14 +13322,14 @@
       <c r="U122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V122" s="9" t="n">
-        <v>0</v>
+      <c r="V122" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X122" s="10" t="n">
-        <v>4</v>
+      <c r="X122" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y122" s="9" t="n">
         <v>0</v>
@@ -13331,17 +13337,13 @@
       <c r="Z122" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA122" s="10" t="n">
-        <v>1</v>
+      <c r="AA122" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB122" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC122" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC122" s="4" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -13355,15 +13357,15 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>7873070</v>
+        <v>5930698</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>NIL Master Talk Toastmasters Club</t>
+          <t>Sarajevo Toastmasters Club</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -13377,13 +13379,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -13391,11 +13393,11 @@
         </is>
       </c>
       <c r="M123" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N123" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O123" s="7" t="inlineStr">
@@ -13421,27 +13423,25 @@
       <c r="U123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V123" s="10" t="n">
+      <c r="V123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X123" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X123" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z123" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB123" s="4" t="n">
-        <v>3</v>
-      </c>
+      <c r="Z123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA123" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB123" s="4" t="n"/>
       <c r="AC123" s="4" t="inlineStr"/>
     </row>
     <row r="124">
@@ -13456,15 +13456,15 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>5930698</v>
+        <v>7549235</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Sarajevo Toastmasters Club</t>
+          <t>Toastmasters Business Club Slovenia</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -13516,32 +13516,38 @@
       <c r="S124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T124" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U124" s="9" t="n">
-        <v>0</v>
+      <c r="T124" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X124" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="9" t="n">
-        <v>0</v>
+      <c r="Z124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA124" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB124" s="4" t="n"/>
-      <c r="AC124" s="4" t="inlineStr"/>
+      <c r="AB124" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC124" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -13555,15 +13561,15 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>7549235</v>
+        <v>1807544</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Business Club Slovenia</t>
+          <t>Toastmasters Ljubljana, Slovenia</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13577,17 +13583,17 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L125" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-10</v>
+      </c>
+      <c r="L125" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M125" s="8" t="n">
@@ -13604,16 +13610,16 @@
         </is>
       </c>
       <c r="P125" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S125" s="9" t="n">
-        <v>0</v>
+      <c r="S125" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T125" s="10" t="n">
         <v>1</v>
@@ -13621,14 +13627,14 @@
       <c r="U125" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V125" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W125" s="9" t="n">
-        <v>0</v>
+      <c r="V125" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W125" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X125" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
@@ -13640,11 +13646,11 @@
         <v>1</v>
       </c>
       <c r="AB125" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC125" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -13660,15 +13666,15 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>1807544</v>
+        <v>7025220</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Ljubljana, Slovenia</t>
+          <t>Toastmasters Villach</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -13682,13 +13688,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="J126" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="J126" s="4" t="n">
-        <v>34</v>
-      </c>
       <c r="K126" s="4" t="n">
-        <v>-11</v>
+        <v>3</v>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
@@ -13709,47 +13715,47 @@
         </is>
       </c>
       <c r="P126" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V126" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q126" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S126" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T126" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U126" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V126" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W126" s="10" t="n">
+      <c r="W126" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X126" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="X126" s="10" t="n">
+      <c r="Y126" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z126" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA126" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB126" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="Y126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z126" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA126" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB126" s="4" t="n">
-        <v>10</v>
-      </c>
       <c r="AC126" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -13761,19 +13767,19 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>7025220</v>
+        <v>28678001</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Villach</t>
+          <t>Anton Paar Speakers' Club</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13787,17 +13793,17 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L127" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L127" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M127" s="8" t="n">
@@ -13825,14 +13831,14 @@
       <c r="S127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T127" s="9" t="n">
-        <v>0</v>
+      <c r="T127" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
@@ -13850,13 +13856,9 @@
         <v>1</v>
       </c>
       <c r="AB127" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC127" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC127" s="4" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -13870,11 +13872,11 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>28678001</v>
+        <v>6560306</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Anton Paar Speakers' Club</t>
+          <t>Erster Grazer Rhetorik Club</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
@@ -13892,17 +13894,17 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K128" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="L128" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L128" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M128" s="8" t="n">
@@ -13928,7 +13930,7 @@
         <v>0</v>
       </c>
       <c r="S128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T128" s="10" t="n">
         <v>1</v>
@@ -13937,13 +13939,13 @@
         <v>0</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X128" s="10" t="n">
-        <v>5</v>
+      <c r="X128" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y128" s="9" t="n">
         <v>0</v>
@@ -13955,9 +13957,13 @@
         <v>1</v>
       </c>
       <c r="AB128" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC128" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC128" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -13971,11 +13977,11 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>6560306</v>
+        <v>3601575</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Erster Grazer Rhetorik Club</t>
+          <t>Toastmasters Rhetorikklub NOE</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
@@ -13993,17 +13999,17 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L129" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L129" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M129" s="8" t="n">
@@ -14029,7 +14035,7 @@
         <v>0</v>
       </c>
       <c r="S129" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T129" s="10" t="n">
         <v>1</v>
@@ -14038,13 +14044,13 @@
         <v>0</v>
       </c>
       <c r="V129" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X129" s="9" t="n">
-        <v>1</v>
+      <c r="X129" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y129" s="9" t="n">
         <v>0</v>
@@ -14056,11 +14062,11 @@
         <v>1</v>
       </c>
       <c r="AB129" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC129" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -14076,15 +14082,15 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>3601575</v>
+        <v>1490250</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Rhetorikklub NOE</t>
+          <t>Wiener Toastmasters Rhetorik Klub</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -14098,17 +14104,17 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L130" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-11</v>
+      </c>
+      <c r="L130" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M130" s="8" t="n">
@@ -14125,31 +14131,31 @@
         </is>
       </c>
       <c r="P130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S130" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q130" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R130" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S130" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T130" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V130" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W130" s="9" t="n">
-        <v>0</v>
+      <c r="U130" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V130" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W130" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X130" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y130" s="9" t="n">
         <v>0</v>
@@ -14161,11 +14167,11 @@
         <v>1</v>
       </c>
       <c r="AB130" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC130" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -14177,19 +14183,19 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>1490250</v>
+        <v>28677693</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Wiener Toastmasters Rhetorik Klub</t>
+          <t>Albanian Leaders Abroad</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -14203,17 +14209,17 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>-14</v>
-      </c>
-      <c r="L131" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L131" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M131" s="8" t="n">
@@ -14230,31 +14236,31 @@
         </is>
       </c>
       <c r="P131" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q131" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R131" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S131" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T131" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U131" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U131" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V131" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W131" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X131" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y131" s="9" t="n">
         <v>0</v>
@@ -14266,13 +14272,9 @@
         <v>1</v>
       </c>
       <c r="AB131" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC131" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC131" s="4" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -14286,15 +14288,15 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>28677693</v>
+        <v>28680202</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Albanian Leaders Abroad</t>
+          <t>Durres Toastmasters Club</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14308,17 +14310,17 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L132" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L132" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M132" s="8" t="n">
@@ -14344,7 +14346,7 @@
         <v>0</v>
       </c>
       <c r="S132" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T132" s="9" t="n">
         <v>0</v>
@@ -14352,8 +14354,8 @@
       <c r="U132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V132" s="10" t="n">
-        <v>4</v>
+      <c r="V132" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="W132" s="9" t="n">
         <v>0</v>
@@ -14371,7 +14373,7 @@
         <v>1</v>
       </c>
       <c r="AB132" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC132" s="4" t="inlineStr"/>
     </row>
@@ -14387,11 +14389,11 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>28680202</v>
+        <v>28680240</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Durres Toastmasters Club</t>
+          <t>Event Speakers Circle</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
@@ -14409,13 +14411,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
@@ -14454,13 +14456,13 @@
         <v>0</v>
       </c>
       <c r="V133" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W133" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X133" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y133" s="9" t="n">
         <v>0</v>
@@ -14488,11 +14490,11 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>28680240</v>
+        <v>28677349</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Event Speakers Circle</t>
+          <t>Toastmasters Tirana</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
@@ -14510,17 +14512,17 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L134" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L134" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M134" s="8" t="n">
@@ -14537,7 +14539,7 @@
         </is>
       </c>
       <c r="P134" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q134" s="9" t="n">
         <v>0</v>
@@ -14546,7 +14548,7 @@
         <v>0</v>
       </c>
       <c r="S134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T134" s="9" t="n">
         <v>0</v>
@@ -14555,13 +14557,13 @@
         <v>0</v>
       </c>
       <c r="V134" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W134" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X134" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y134" s="9" t="n">
         <v>0</v>
@@ -14573,31 +14575,35 @@
         <v>1</v>
       </c>
       <c r="AB134" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC134" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC134" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>28677349</v>
+        <v>28680385</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Tirana</t>
+          <t>Adana Toastmasters</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -14611,17 +14617,17 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L135" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L135" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M135" s="8" t="n">
@@ -14638,7 +14644,7 @@
         </is>
       </c>
       <c r="P135" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q135" s="9" t="n">
         <v>0</v>
@@ -14647,7 +14653,7 @@
         <v>0</v>
       </c>
       <c r="S135" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T135" s="9" t="n">
         <v>0</v>
@@ -14656,31 +14662,27 @@
         <v>0</v>
       </c>
       <c r="V135" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W135" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X135" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z135" s="10" t="n">
-        <v>1</v>
+      <c r="Z135" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA135" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB135" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC135" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC135" s="4" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -14694,15 +14696,15 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>28680385</v>
+        <v>5220048</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Adana Toastmasters</t>
+          <t>Ankara Business Toastmasters</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14716,17 +14718,17 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L136" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M136" s="8" t="n">
@@ -14760,28 +14762,32 @@
       <c r="U136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V136" s="9" t="n">
-        <v>0</v>
+      <c r="V136" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X136" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="9" t="n">
-        <v>0</v>
+      <c r="Z136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA136" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB136" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC136" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC136" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -14795,15 +14801,15 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>5220048</v>
+        <v>7110318</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Ankara Business Toastmasters</t>
+          <t>Ankara Kolejliler Toastmasters</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -14817,13 +14823,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -14861,30 +14867,30 @@
       <c r="U137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V137" s="10" t="n">
-        <v>4</v>
+      <c r="V137" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W137" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X137" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z137" s="10" t="n">
-        <v>1</v>
+      <c r="Z137" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA137" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB137" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC137" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -14900,15 +14906,15 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>7110318</v>
+        <v>6579</v>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Ankara Kolejliler Toastmasters</t>
+          <t>Ankara Toastmasters</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14922,10 +14928,10 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="K138" s="4" t="n">
         <v>-11</v>
@@ -14949,7 +14955,7 @@
         </is>
       </c>
       <c r="P138" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q138" s="9" t="n">
         <v>0</v>
@@ -14967,29 +14973,29 @@
         <v>0</v>
       </c>
       <c r="V138" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X138" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="9" t="n">
-        <v>0</v>
+      <c r="Z138" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA138" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB138" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AC138" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -15005,15 +15011,15 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>6579</v>
+        <v>2979303</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Ankara Toastmasters</t>
+          <t>Ankara Turkce Toastmasters</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -15027,13 +15033,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J139" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>-12</v>
+        <v>-3</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -15054,7 +15060,7 @@
         </is>
       </c>
       <c r="P139" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q139" s="9" t="n">
         <v>0</v>
@@ -15063,16 +15069,16 @@
         <v>0</v>
       </c>
       <c r="S139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T139" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T139" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U139" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
@@ -15090,7 +15096,7 @@
         <v>1</v>
       </c>
       <c r="AB139" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC139" s="4" t="inlineStr">
         <is>
@@ -15106,19 +15112,19 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>2979303</v>
+        <v>28675799</v>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Ankara Turkce Toastmasters</t>
+          <t>Anatolia Toastmasters</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -15132,13 +15138,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-3</v>
+        <v>-10</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -15170,26 +15176,26 @@
       <c r="S140" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T140" s="10" t="n">
-        <v>1</v>
+      <c r="T140" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U140" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V140" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W140" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X140" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z140" s="10" t="n">
-        <v>1</v>
+      <c r="Z140" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA140" s="10" t="n">
         <v>1</v>
@@ -15215,15 +15221,15 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>28675799</v>
+        <v>4863037</v>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Anatolia Toastmasters</t>
+          <t>Bosphorus Toastmasters</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -15237,13 +15243,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>-11</v>
+        <v>-6</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -15264,37 +15270,37 @@
         </is>
       </c>
       <c r="P141" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q141" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S141" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T141" s="9" t="n">
-        <v>0</v>
+      <c r="S141" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T141" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U141" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V141" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W141" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X141" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="9" t="n">
-        <v>0</v>
+      <c r="Z141" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA141" s="10" t="n">
         <v>1</v>
@@ -15320,15 +15326,15 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>4863037</v>
+        <v>2883886</v>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Bosphorus Toastmasters</t>
+          <t>Istanbul Asia Toastmasters</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -15342,13 +15348,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -15369,28 +15375,28 @@
         </is>
       </c>
       <c r="P142" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q142" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R142" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S142" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T142" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="T142" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V142" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W142" s="9" t="n">
-        <v>0</v>
+      <c r="V142" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W142" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X142" s="10" t="n">
         <v>5</v>
@@ -15405,11 +15411,11 @@
         <v>1</v>
       </c>
       <c r="AB142" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC142" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -15425,11 +15431,11 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>2883886</v>
+        <v>1042863</v>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Istanbul Asia Toastmasters</t>
+          <t>Istanbul Toastmasters</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
@@ -15447,17 +15453,17 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L143" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-9</v>
+      </c>
+      <c r="L143" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M143" s="8" t="n">
@@ -15474,7 +15480,7 @@
         </is>
       </c>
       <c r="P143" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q143" s="9" t="n">
         <v>0</v>
@@ -15482,11 +15488,11 @@
       <c r="R143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S143" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T143" s="9" t="n">
-        <v>0</v>
+      <c r="S143" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T143" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U143" s="9" t="n">
         <v>0</v>
@@ -15495,10 +15501,10 @@
         <v>4</v>
       </c>
       <c r="W143" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X143" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y143" s="9" t="n">
         <v>0</v>
@@ -15510,11 +15516,11 @@
         <v>1</v>
       </c>
       <c r="AB143" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC143" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -15526,19 +15532,19 @@
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>1042863</v>
+        <v>4966081</v>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Istanbul Toastmasters</t>
+          <t>Anadolu Toastmasters</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -15552,13 +15558,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J144" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="J144" s="4" t="n">
-        <v>37</v>
-      </c>
       <c r="K144" s="4" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
@@ -15582,7 +15588,7 @@
         <v>1</v>
       </c>
       <c r="Q144" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R144" s="9" t="n">
         <v>0</v>
@@ -15590,17 +15596,17 @@
       <c r="S144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T144" s="10" t="n">
-        <v>1</v>
+      <c r="T144" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V144" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W144" s="10" t="n">
-        <v>5</v>
+      <c r="V144" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W144" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X144" s="10" t="n">
         <v>7</v>
@@ -15635,11 +15641,11 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>4966081</v>
+        <v>28677753</v>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Anadolu Toastmasters</t>
+          <t>Bodrum Toastmasters</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
@@ -15657,25 +15663,25 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J145" s="4" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L145" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L145" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M145" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N145" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O145" s="7" t="inlineStr">
@@ -15684,10 +15690,10 @@
         </is>
       </c>
       <c r="P145" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q145" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R145" s="9" t="n">
         <v>0</v>
@@ -15701,8 +15707,8 @@
       <c r="U145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V145" s="9" t="n">
-        <v>2</v>
+      <c r="V145" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W145" s="9" t="n">
         <v>0</v>
@@ -15716,17 +15722,13 @@
       <c r="Z145" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA145" s="10" t="n">
-        <v>1</v>
+      <c r="AA145" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB145" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC145" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC145" s="4" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
@@ -15740,15 +15742,15 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>28677753</v>
+        <v>2548956</v>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Bodrum Toastmasters</t>
+          <t>Istanbul Turkce Toastmasters</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -15762,13 +15764,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
@@ -15776,11 +15778,11 @@
         </is>
       </c>
       <c r="M146" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N146" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O146" s="7" t="inlineStr">
@@ -15792,7 +15794,7 @@
         <v>0</v>
       </c>
       <c r="Q146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R146" s="9" t="n">
         <v>0</v>
@@ -15821,13 +15823,17 @@
       <c r="Z146" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA146" s="9" t="n">
-        <v>0</v>
+      <c r="AA146" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB146" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC146" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC146" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -15841,15 +15847,15 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>2548956</v>
+        <v>7173891</v>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Istanbul Turkce Toastmasters</t>
+          <t>Izmir Türkçe Toastmasters</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -15863,13 +15869,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J147" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
@@ -15892,23 +15898,23 @@
       <c r="P147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q147" s="9" t="n">
-        <v>1</v>
+      <c r="Q147" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R147" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S147" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T147" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T147" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V147" s="9" t="n">
-        <v>3</v>
+      <c r="V147" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W147" s="9" t="n">
         <v>0</v>
@@ -15926,11 +15932,11 @@
         <v>1</v>
       </c>
       <c r="AB147" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC147" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -15946,15 +15952,15 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>7173891</v>
+        <v>28679541</v>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Izmir Türkçe Toastmasters</t>
+          <t>Smyrna Toastmasters</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>10</v>
@@ -15968,17 +15974,17 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J148" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L148" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L148" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M148" s="8" t="n">
@@ -15997,47 +16003,41 @@
       <c r="P148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" s="10" t="n">
-        <v>2</v>
+      <c r="Q148" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R148" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S148" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T148" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T148" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V148" s="10" t="n">
-        <v>4</v>
+      <c r="V148" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X148" s="10" t="n">
-        <v>7</v>
+      <c r="X148" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z148" s="10" t="n">
-        <v>1</v>
+      <c r="Z148" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA148" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB148" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC148" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+      <c r="AB148" s="4" t="n"/>
+      <c r="AC148" s="4" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -16459,7 +16459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -16601,7 +16601,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -16766,7 +16766,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -16886,25 +16886,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -16924,7 +16924,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -16943,10 +16943,10 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -16957,29 +16957,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -16990,47 +16990,47 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>4</v>
       </c>
       <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
         <v>2</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>3</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -17042,10 +17042,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -17056,14 +17056,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -17078,7 +17078,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -17089,29 +17089,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -17122,11 +17122,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
@@ -17135,13 +17135,13 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>3</v>
@@ -17150,19 +17150,19 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -17177,7 +17177,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -17188,29 +17188,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -17221,29 +17221,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -17254,14 +17254,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -17276,7 +17276,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -17287,26 +17287,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>2</v>
@@ -17315,34 +17315,34 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1.2</v>
+        <v>1.75</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -17353,14 +17353,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -17375,7 +17375,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -17386,17 +17386,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
         <v>4</v>
@@ -17405,10 +17405,10 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -17419,26 +17419,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>2</v>
@@ -17452,20 +17452,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>3.25</v>
+        <v>1.25</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -17480,25 +17480,25 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -17507,7 +17507,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -17518,20 +17518,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>2.75</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -17551,29 +17551,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>2.75</v>
+        <v>1.4</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -17584,14 +17584,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -17609,41 +17609,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>4</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>4</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I35"/>
+  <autoFilter ref="A1:I34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>